--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table64.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table64.xlsx
@@ -118,9 +118,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
-    <numFmt numFmtId="168" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
-    <numFmt numFmtId="169" formatCode="#\ ??/12"/>
-    <numFmt numFmtId="170" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="#\ ??/12"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -191,7 +191,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -240,6 +240,12 @@
         <bgColor indexed="8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="35">
     <border>
@@ -662,52 +668,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="39" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="4" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="170" fontId="6" fillId="4" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="6" fillId="4" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="39" fontId="5" fillId="3" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -720,49 +726,52 @@
     <xf numFmtId="39" fontId="3" fillId="2" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="2" borderId="13" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="13" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="3" fillId="2" borderId="14" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="2" borderId="15" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="15" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="5" fillId="3" borderId="16" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="39" fontId="3" fillId="3" borderId="17" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="3" borderId="18" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="18" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="3" fillId="3" borderId="19" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="3" borderId="20" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="20" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="8" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="8" fillId="6" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="7" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="39" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="8" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="8" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="39" fontId="8" fillId="6" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="7" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="39" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="39" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="4" fillId="8" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -774,21 +783,18 @@
     <xf numFmtId="39" fontId="4" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="39" fontId="4" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="39" fontId="4" fillId="9" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="5" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="5" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="170" fontId="7" fillId="5" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="170" fontId="7" fillId="5" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="170" fontId="7" fillId="5" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1279,29 +1285,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.5">
-      <c r="A1" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="A1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
     </row>
     <row r="2" spans="1:8" ht="17.5">
-      <c r="A2" s="34">
+      <c r="A2" s="45">
         <f>A3</f>
         <v>41973</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1">
@@ -1316,40 +1322,40 @@
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="42"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="46" t="s">
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="49"/>
     </row>
     <row r="5" spans="1:8" ht="25.5">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="39" t="s">
+      <c r="F5" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="39" t="s">
+      <c r="G5" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="H5" s="38" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2528,7 +2534,7 @@
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="49" t="s">
+      <c r="A56" s="56" t="s">
         <v>27</v>
       </c>
       <c r="B56" s="50"/>
